--- a/data/trans_orig/IP07KS_C04_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C04_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse solo/a en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse solo/a, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4846</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2393</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6579</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5924</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12580</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7046</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27328</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19934</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36034</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24740</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18220</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31252</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26273</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19203</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32825</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>36,69%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>26,82%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26633</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19455</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>35777</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51374</t>
+          <t>53601</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>43099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>65281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54573</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71355</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>35942</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29010</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42465</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>31138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72957</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>101001</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89276</t>
+          <t>89559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111619</t>
+          <t>112332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1564</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1896</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5793</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6357</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1789</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6225</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4194</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2365</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6737</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12008</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20383</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7036</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12490</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>28730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63782</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49131</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78529</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57510</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34942</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>95980</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>67,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>35740</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44950</t>
+          <t>27343</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77834</t>
+          <t>46992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>119768</t>
+          <t>99522</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93638</t>
+          <t>83640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171450</t>
+          <t>115723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93005</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78935</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>111047</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>74072</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39406</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>94202</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>51,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96603</t>
+          <t>77818</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81087</t>
+          <t>67417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116327</t>
+          <t>87487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>170675</t>
+          <t>170824</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124282</t>
+          <t>153533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196306</t>
+          <t>189298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9614</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28554</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16713</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>91110</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>73827</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>109547</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>82250</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>58789</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>129707</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88892</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>75555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>153123</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>131210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>229586</t>
+          <t>172989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>156391</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>138290</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>173545</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>64,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>110014</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>69990</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>130953</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>161662</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142272</t>
+          <t>103072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182435</t>
+          <t>127424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>271676</t>
+          <t>272038</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297525</t>
+          <t>296114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>577</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
